--- a/public/templates/AnakAktaKelahiran.xlsx
+++ b/public/templates/AnakAktaKelahiran.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wamp64\www\dinsos-sipandakabulan-ci4\public\template_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC3A99F-C424-4988-818C-C04268AA4E77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57EF99D0-9CDA-4E1A-85C2-BDFA8DEA6C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0D47A6A9-629B-4A61-AB30-EB2735FC9B95}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0D47A6A9-629B-4A61-AB30-EB2735FC9B95}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,12 +42,6 @@
     <t>Kategori Umur</t>
   </si>
   <si>
-    <t>Tahun 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tahun 2022</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jumlah anak </t>
   </si>
   <si>
@@ -76,6 +73,12 @@
   </si>
   <si>
     <t>12 - &lt; 18 tahun</t>
+  </si>
+  <si>
+    <t>Tahun 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tahun 2025</t>
   </si>
 </sst>
 </file>
@@ -279,58 +282,10 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -341,6 +296,54 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,321 +660,316 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44ADFE81-1BAF-4C00-B01C-A23013ED9FE4}">
   <dimension ref="A2:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="11"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="4" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="6"/>
+      <c r="G3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="11"/>
+      <c r="M3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="11"/>
+      <c r="P3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="4" t="s">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="9"/>
+      <c r="N4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4">
+        <f>D5+E5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4">
+        <f>G5+H5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <f>F5*I5/100</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="4">
+        <f>K5+L5</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="4">
+        <f>N5+O5</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <f>O5*P5/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4">
+        <f>D6+E6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4">
+        <f>G6+H6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <f>F6*I6/100</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="4">
+        <f t="shared" ref="M6:M9" si="0">K6+L6</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="4">
+        <f t="shared" ref="P6:P9" si="1">N6+O6</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <f>O6+P6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4">
+        <f>D7+E7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4">
+        <f>G7+H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <f>F7*I7/100</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <f>O7+P7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="9" t="s">
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4">
+        <f>D8+E8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4">
+        <f>G8+H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <f>F8*I8/100</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <f>O8+P8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="15"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="16">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20">
-        <f>D5+E5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="20">
-        <f>G5+H5</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="20">
-        <f>F5*I5/100</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20">
-        <f>K5+L5</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="20">
-        <f>N5+O5</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="21">
-        <f>O5*P5/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="16">
-        <v>2</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="20">
-        <f>D6+E6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="20">
-        <f>G6+H6</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="20">
-        <f>F6*I6/100</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="20">
-        <f t="shared" ref="M6:M9" si="0">K6+L6</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="20">
-        <f t="shared" ref="P6:P9" si="1">N6+O6</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="21">
-        <f>O6+P6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="16">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20">
-        <f>D7+E7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="20">
-        <f>G7+H7</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="20">
-        <f>F7*I7/100</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="20">
+      <c r="C9" s="7"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4">
+        <f>D9+E9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4">
+        <f>G9+H9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <f>F9*I9/100</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="20">
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="21">
-        <f>O7+P7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="16">
-        <v>4</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20">
-        <f>D8+E8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20">
-        <f>G8+H8</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="20">
-        <f>F8*I8/100</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="21">
-        <f>O8+P8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="16">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20">
-        <f>D9+E9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20">
-        <f>G9+H9</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="20">
-        <f>F9*I9/100</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="5">
         <f>O9+P9</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:O3"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="B5:C5"/>
@@ -986,6 +984,11 @@
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:L3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
